--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,7 +367,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -630,7 +630,7 @@
     <t>Composition.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1028,7 +1028,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition)</t>
+Reference(Composition|4.0.1)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -1217,13 +1217,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1309,7 +1309,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1355,7 +1355,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>

--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-composition.xlsx
+++ b/fhir/StructureDefinition-ehealth-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
